--- a/Versão5/PRO/Ontologia_Fabricantes.xlsx
+++ b/Versão5/PRO/Ontologia_Fabricantes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2861FAD-05B0-4E9B-A250-034201FC4A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42718EFE-6F21-413C-BDB6-5C5469D07A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -3374,59 +3374,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <b val="0"/>
@@ -3848,15 +3796,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="10.3046875" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3867,7 +3815,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -3878,7 +3826,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -3889,7 +3837,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3900,7 +3848,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -3912,7 +3860,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -3924,7 +3872,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -3935,7 +3883,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="34" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="34" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -3946,7 +3894,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -3957,7 +3905,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -3968,7 +3916,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -3979,7 +3927,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -3990,7 +3938,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -4001,7 +3949,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -4012,7 +3960,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -4023,7 +3971,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -4034,7 +3982,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -4045,19 +3993,19 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46259.684071990741</v>
+        <v>46264.568499652778</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -4068,7 +4016,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -4079,7 +4027,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -4090,7 +4038,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
@@ -4101,7 +4049,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
@@ -4113,7 +4061,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="34" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="34" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>83</v>
       </c>
@@ -4133,37 +4081,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <dimension ref="A1:AC150"/>
-  <sheetFormatPr defaultColWidth="2.7109375" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.69140625" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="56" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" style="56" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.84375" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.53515625" style="31" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.3828125" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.84375" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.84375" style="31" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="37" style="31" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="40.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="32.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.140625" style="31" customWidth="1"/>
-    <col min="20" max="20" width="6.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="40.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.15234375" style="31" customWidth="1"/>
+    <col min="20" max="20" width="6.84375" style="31" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.84375" style="31" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="7" style="31" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.5703125" style="31" customWidth="1"/>
-    <col min="27" max="27" width="5.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.85546875" style="31" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="2.7109375" style="31"/>
+    <col min="26" max="26" width="7.53515625" style="31" customWidth="1"/>
+    <col min="27" max="27" width="5.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.84375" style="31" customWidth="1"/>
+    <col min="29" max="29" width="15.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="2.69140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="34" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="55">
         <v>0</v>
       </c>
@@ -4252,7 +4200,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="41" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" s="41" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="48">
         <v>2</v>
       </c>
@@ -4349,7 +4297,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="48">
         <v>3</v>
       </c>
@@ -4446,7 +4394,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="48">
         <v>4</v>
       </c>
@@ -4536,7 +4484,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="48">
         <v>5</v>
       </c>
@@ -4633,7 +4581,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="48">
         <v>6</v>
       </c>
@@ -4730,7 +4678,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="48">
         <v>7</v>
       </c>
@@ -4827,7 +4775,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="48">
         <v>8</v>
       </c>
@@ -4924,7 +4872,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="48">
         <v>9</v>
       </c>
@@ -5021,7 +4969,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="48">
         <v>10</v>
       </c>
@@ -5118,7 +5066,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="48">
         <v>11</v>
       </c>
@@ -5215,7 +5163,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="48">
         <v>12</v>
       </c>
@@ -5312,7 +5260,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="48">
         <v>13</v>
       </c>
@@ -5402,7 +5350,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="48">
         <v>14</v>
       </c>
@@ -5499,7 +5447,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="48">
         <v>15</v>
       </c>
@@ -5596,7 +5544,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="48">
         <v>16</v>
       </c>
@@ -5693,7 +5641,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="48">
         <v>17</v>
       </c>
@@ -5790,7 +5738,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="48">
         <v>18</v>
       </c>
@@ -5887,7 +5835,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="48">
         <v>19</v>
       </c>
@@ -5984,7 +5932,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="48">
         <v>20</v>
       </c>
@@ -6081,7 +6029,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="48">
         <v>21</v>
       </c>
@@ -6178,7 +6126,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="48">
         <v>22</v>
       </c>
@@ -6268,7 +6216,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="48">
         <v>23</v>
       </c>
@@ -6365,7 +6313,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="48">
         <v>24</v>
       </c>
@@ -6462,7 +6410,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="48">
         <v>25</v>
       </c>
@@ -6559,7 +6507,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="48">
         <v>26</v>
       </c>
@@ -6656,7 +6604,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="48">
         <v>27</v>
       </c>
@@ -6753,7 +6701,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="48">
         <v>28</v>
       </c>
@@ -6850,7 +6798,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="48">
         <v>29</v>
       </c>
@@ -6947,7 +6895,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="48">
         <v>30</v>
       </c>
@@ -7044,7 +6992,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="48">
         <v>31</v>
       </c>
@@ -7134,7 +7082,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="48">
         <v>32</v>
       </c>
@@ -7231,7 +7179,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="48">
         <v>33</v>
       </c>
@@ -7328,7 +7276,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="48">
         <v>34</v>
       </c>
@@ -7425,7 +7373,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="48">
         <v>35</v>
       </c>
@@ -7522,7 +7470,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="48">
         <v>36</v>
       </c>
@@ -7619,7 +7567,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="48">
         <v>37</v>
       </c>
@@ -7716,7 +7664,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="48">
         <v>38</v>
       </c>
@@ -7813,7 +7761,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="48">
         <v>39</v>
       </c>
@@ -7910,7 +7858,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="48">
         <v>40</v>
       </c>
@@ -8000,7 +7948,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="48">
         <v>41</v>
       </c>
@@ -8097,7 +8045,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="48">
         <v>42</v>
       </c>
@@ -8194,7 +8142,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="48">
         <v>43</v>
       </c>
@@ -8291,7 +8239,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="48">
         <v>44</v>
       </c>
@@ -8388,7 +8336,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="48">
         <v>45</v>
       </c>
@@ -8485,7 +8433,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="48">
         <v>46</v>
       </c>
@@ -8582,7 +8530,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="48">
         <v>47</v>
       </c>
@@ -8679,7 +8627,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="48">
         <v>48</v>
       </c>
@@ -8776,7 +8724,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="48">
         <v>49</v>
       </c>
@@ -8866,7 +8814,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="48">
         <v>50</v>
       </c>
@@ -8963,7 +8911,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="48">
         <v>51</v>
       </c>
@@ -9060,7 +9008,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="48">
         <v>52</v>
       </c>
@@ -9157,7 +9105,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="48">
         <v>53</v>
       </c>
@@ -9254,7 +9202,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="48">
         <v>54</v>
       </c>
@@ -9351,7 +9299,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="48">
         <v>55</v>
       </c>
@@ -9448,7 +9396,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="48">
         <v>56</v>
       </c>
@@ -9545,7 +9493,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="48">
         <v>57</v>
       </c>
@@ -9642,7 +9590,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="48">
         <v>58</v>
       </c>
@@ -9732,7 +9680,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="48">
         <v>59</v>
       </c>
@@ -9829,7 +9777,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="48">
         <v>60</v>
       </c>
@@ -9926,7 +9874,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="48">
         <v>61</v>
       </c>
@@ -10023,7 +9971,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="48">
         <v>62</v>
       </c>
@@ -10120,7 +10068,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="48">
         <v>63</v>
       </c>
@@ -10217,7 +10165,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="48">
         <v>64</v>
       </c>
@@ -10314,7 +10262,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="48">
         <v>65</v>
       </c>
@@ -10411,7 +10359,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="48">
         <v>66</v>
       </c>
@@ -10508,7 +10456,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="48">
         <v>67</v>
       </c>
@@ -10598,7 +10546,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="48">
         <v>68</v>
       </c>
@@ -10695,7 +10643,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="48">
         <v>69</v>
       </c>
@@ -10792,7 +10740,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="48">
         <v>70</v>
       </c>
@@ -10889,7 +10837,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="48">
         <v>71</v>
       </c>
@@ -10986,7 +10934,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="48">
         <v>72</v>
       </c>
@@ -11083,7 +11031,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="48">
         <v>73</v>
       </c>
@@ -11180,7 +11128,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="48">
         <v>74</v>
       </c>
@@ -11277,7 +11225,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="48">
         <v>75</v>
       </c>
@@ -11374,7 +11322,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="48">
         <v>76</v>
       </c>
@@ -11464,7 +11412,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="48">
         <v>77</v>
       </c>
@@ -11561,7 +11509,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="48">
         <v>78</v>
       </c>
@@ -11658,7 +11606,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="48">
         <v>79</v>
       </c>
@@ -11755,7 +11703,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="48">
         <v>80</v>
       </c>
@@ -11852,7 +11800,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="48">
         <v>81</v>
       </c>
@@ -11949,7 +11897,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="48">
         <v>82</v>
       </c>
@@ -12046,7 +11994,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="48">
         <v>83</v>
       </c>
@@ -12143,7 +12091,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="48">
         <v>84</v>
       </c>
@@ -12240,7 +12188,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="48">
         <v>85</v>
       </c>
@@ -12330,7 +12278,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="48">
         <v>86</v>
       </c>
@@ -12427,7 +12375,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="48">
         <v>87</v>
       </c>
@@ -12524,7 +12472,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="48">
         <v>88</v>
       </c>
@@ -12621,7 +12569,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="48">
         <v>89</v>
       </c>
@@ -12718,7 +12666,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="48">
         <v>90</v>
       </c>
@@ -12815,7 +12763,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="48">
         <v>91</v>
       </c>
@@ -12912,7 +12860,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="48">
         <v>92</v>
       </c>
@@ -13009,7 +12957,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="48">
         <v>93</v>
       </c>
@@ -13106,7 +13054,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="48">
         <v>94</v>
       </c>
@@ -13196,7 +13144,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="48">
         <v>95</v>
       </c>
@@ -13293,7 +13241,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="48">
         <v>96</v>
       </c>
@@ -13390,7 +13338,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="48">
         <v>97</v>
       </c>
@@ -13487,7 +13435,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="48">
         <v>98</v>
       </c>
@@ -13584,7 +13532,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="48">
         <v>99</v>
       </c>
@@ -13681,7 +13629,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="48">
         <v>100</v>
       </c>
@@ -13778,7 +13726,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="48">
         <v>101</v>
       </c>
@@ -13875,7 +13823,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="48">
         <v>102</v>
       </c>
@@ -13972,7 +13920,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="48">
         <v>103</v>
       </c>
@@ -14062,7 +14010,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="48">
         <v>104</v>
       </c>
@@ -14159,7 +14107,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="48">
         <v>105</v>
       </c>
@@ -14256,7 +14204,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="48">
         <v>106</v>
       </c>
@@ -14353,7 +14301,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="48">
         <v>107</v>
       </c>
@@ -14450,7 +14398,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="48">
         <v>108</v>
       </c>
@@ -14547,7 +14495,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="48">
         <v>109</v>
       </c>
@@ -14644,7 +14592,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="48">
         <v>110</v>
       </c>
@@ -14741,7 +14689,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="48">
         <v>111</v>
       </c>
@@ -14838,7 +14786,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="48">
         <v>112</v>
       </c>
@@ -14928,7 +14876,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="48">
         <v>113</v>
       </c>
@@ -15025,7 +14973,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="48">
         <v>114</v>
       </c>
@@ -15122,7 +15070,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="48">
         <v>115</v>
       </c>
@@ -15219,7 +15167,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="48">
         <v>116</v>
       </c>
@@ -15316,7 +15264,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="48">
         <v>117</v>
       </c>
@@ -15413,7 +15361,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="48">
         <v>118</v>
       </c>
@@ -15510,7 +15458,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="48">
         <v>119</v>
       </c>
@@ -15607,7 +15555,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="48">
         <v>120</v>
       </c>
@@ -15704,7 +15652,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="48">
         <v>121</v>
       </c>
@@ -15801,7 +15749,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="48">
         <v>122</v>
       </c>
@@ -15898,7 +15846,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="48">
         <v>123</v>
       </c>
@@ -15995,7 +15943,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="48">
         <v>124</v>
       </c>
@@ -16092,7 +16040,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="48">
         <v>125</v>
       </c>
@@ -16189,7 +16137,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="48">
         <v>126</v>
       </c>
@@ -16286,7 +16234,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="48">
         <v>127</v>
       </c>
@@ -16383,7 +16331,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="48">
         <v>128</v>
       </c>
@@ -16480,7 +16428,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="48">
         <v>129</v>
       </c>
@@ -16577,7 +16525,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="48">
         <v>130</v>
       </c>
@@ -16674,7 +16622,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="48">
         <v>131</v>
       </c>
@@ -16771,7 +16719,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="48">
         <v>132</v>
       </c>
@@ -16868,7 +16816,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="48">
         <v>133</v>
       </c>
@@ -16965,7 +16913,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="48">
         <v>134</v>
       </c>
@@ -17062,7 +17010,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="48">
         <v>135</v>
       </c>
@@ -17159,7 +17107,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="48">
         <v>136</v>
       </c>
@@ -17256,7 +17204,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="48">
         <v>137</v>
       </c>
@@ -17353,7 +17301,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="138" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="48">
         <v>138</v>
       </c>
@@ -17450,7 +17398,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="139" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="48">
         <v>139</v>
       </c>
@@ -17547,7 +17495,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="140" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="48">
         <v>140</v>
       </c>
@@ -17644,7 +17592,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="141" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="48">
         <v>141</v>
       </c>
@@ -17741,7 +17689,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="142" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="48">
         <v>142</v>
       </c>
@@ -17838,7 +17786,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="143" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="48">
         <v>143</v>
       </c>
@@ -17935,7 +17883,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="144" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="48">
         <v>144</v>
       </c>
@@ -18032,7 +17980,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="145" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="48">
         <v>145</v>
       </c>
@@ -18129,7 +18077,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="146" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="48">
         <v>146</v>
       </c>
@@ -18226,7 +18174,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="147" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="48">
         <v>147</v>
       </c>
@@ -18323,7 +18271,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="148" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="48">
         <v>148</v>
       </c>
@@ -18420,7 +18368,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="149" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="48">
         <v>149</v>
       </c>
@@ -18517,7 +18465,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="150" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="48">
         <v>150</v>
       </c>
@@ -18528,10 +18476,10 @@
         <v>888</v>
       </c>
       <c r="D150" s="59" t="s">
+        <v>890</v>
+      </c>
+      <c r="E150" s="59" t="s">
         <v>889</v>
-      </c>
-      <c r="E150" s="59" t="s">
-        <v>890</v>
       </c>
       <c r="F150" s="59" t="s">
         <v>891</v>
@@ -18557,11 +18505,11 @@
       </c>
       <c r="M150" s="60" t="str">
         <f t="shared" si="62"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N150" s="60" t="str">
         <f t="shared" si="62"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O150" s="60" t="str">
         <f t="shared" si="62"/>
@@ -18585,11 +18533,11 @@
       </c>
       <c r="U150" s="33" t="str">
         <f t="shared" si="59"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V150" s="61" t="str">
         <f t="shared" si="59"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W150" s="33" t="s">
         <v>176</v>
@@ -18620,19 +18568,19 @@
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="A2:B150">
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F150">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F1048576 F1:F149">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R150">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18643,16 +18591,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="5.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.7109375" style="21"/>
+    <col min="1" max="1" width="1.3046875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.53515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="5.15234375" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="5.69140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.2">
       <c r="A1" s="19">
         <v>1</v>
       </c>
@@ -18717,7 +18665,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -18790,16 +18738,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.140625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="1.3828125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.15234375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="7.3828125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="7.69140625" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -18813,7 +18761,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -18835,38 +18783,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D50BAA-DAEA-47D5-8FAA-A68A87918655}">
   <dimension ref="A1:AI37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="38" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" style="38" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" style="38" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="10.3046875" style="38" customWidth="1"/>
+    <col min="3" max="3" width="8.15234375" style="38" customWidth="1"/>
     <col min="4" max="4" width="8" style="38" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" style="38" customWidth="1"/>
+    <col min="5" max="5" width="6.84375" style="38" customWidth="1"/>
     <col min="6" max="6" width="6" style="41" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.140625" style="41" customWidth="1"/>
+    <col min="7" max="7" width="39.15234375" style="41" customWidth="1"/>
     <col min="8" max="8" width="10" style="41" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" style="42" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="67.85546875" style="41" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="65.85546875" style="41" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.28515625" style="41" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.85546875" style="41" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.85546875" style="38" customWidth="1"/>
-    <col min="24" max="24" width="6.5703125" style="38" customWidth="1"/>
-    <col min="25" max="25" width="8.140625" style="38" customWidth="1"/>
-    <col min="26" max="35" width="3.7109375" style="38" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="38"/>
+    <col min="9" max="9" width="17.3828125" style="42" customWidth="1"/>
+    <col min="10" max="10" width="7.69140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="67.84375" style="41" customWidth="1"/>
+    <col min="12" max="12" width="8.3046875" style="38" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="65.84375" style="41" customWidth="1"/>
+    <col min="14" max="14" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.84375" style="41" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.84375" style="41" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.3046875" style="41" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.84375" style="41" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" style="38" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.84375" style="41" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.3046875" style="38" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.84375" style="38" customWidth="1"/>
+    <col min="24" max="24" width="6.53515625" style="38" customWidth="1"/>
+    <col min="25" max="25" width="8.15234375" style="38" customWidth="1"/>
+    <col min="26" max="35" width="3.69140625" style="38" customWidth="1"/>
+    <col min="36" max="16384" width="9.15234375" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -18973,7 +18921,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -19080,7 +19028,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16">
         <v>3</v>
       </c>
@@ -19187,7 +19135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16">
         <v>4</v>
       </c>
@@ -19294,7 +19242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16">
         <v>5</v>
       </c>
@@ -19401,7 +19349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16">
         <v>6</v>
       </c>
@@ -19508,7 +19456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16">
         <v>7</v>
       </c>
@@ -19615,7 +19563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16">
         <v>8</v>
       </c>
@@ -19722,7 +19670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="16">
         <v>9</v>
       </c>
@@ -19829,7 +19777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16">
         <v>10</v>
       </c>
@@ -19936,7 +19884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16">
         <v>11</v>
       </c>
@@ -20043,7 +19991,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="16">
         <v>12</v>
       </c>
@@ -20150,7 +20098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="16">
         <v>13</v>
       </c>
@@ -20257,7 +20205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="16">
         <v>14</v>
       </c>
@@ -20364,7 +20312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="16">
         <v>15</v>
       </c>
@@ -20471,7 +20419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="16">
         <v>16</v>
       </c>
@@ -20578,7 +20526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="16">
         <v>17</v>
       </c>
@@ -20685,7 +20633,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="16">
         <v>18</v>
       </c>
@@ -20792,7 +20740,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16">
         <v>19</v>
       </c>
@@ -20899,7 +20847,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16">
         <v>20</v>
       </c>
@@ -21006,7 +20954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16">
         <v>21</v>
       </c>
@@ -21113,7 +21061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="16">
         <v>22</v>
       </c>
@@ -21220,7 +21168,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="16">
         <v>23</v>
       </c>
@@ -21327,7 +21275,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -21434,7 +21382,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16">
         <v>25</v>
       </c>
@@ -21541,7 +21489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16">
         <v>26</v>
       </c>
@@ -21648,7 +21596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="16">
         <v>27</v>
       </c>
@@ -21755,7 +21703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="16">
         <v>28</v>
       </c>
@@ -21862,7 +21810,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="16">
         <v>29</v>
       </c>
@@ -21969,7 +21917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="16">
         <v>30</v>
       </c>
@@ -22076,7 +22024,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="16">
         <v>31</v>
       </c>
@@ -22183,7 +22131,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="16">
         <v>32</v>
       </c>
@@ -22290,7 +22238,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:35" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:35" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>33</v>
       </c>
@@ -22398,7 +22346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:35" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:35" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>34</v>
       </c>
@@ -22506,7 +22454,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:35" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:35" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>35</v>
       </c>
@@ -22614,7 +22562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:35" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:35" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>36</v>
       </c>
@@ -22722,7 +22670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:35" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:35" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>37</v>
       </c>
@@ -22836,11 +22784,11 @@
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="B1:B32 B38:B1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B32 B1 B5:B23">
-    <cfRule type="duplicateValues" dxfId="10" priority="563"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="564"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>

--- a/Versão5/PRO/Ontologia_Fabricantes.xlsx
+++ b/Versão5/PRO/Ontologia_Fabricantes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA1E475-3E82-4B90-902E-BC436D558E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D28D44B-8827-4F5D-A982-184953004442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4700" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4700" uniqueCount="937">
   <si>
     <t>Edição</t>
   </si>
@@ -2747,9 +2747,6 @@
   </si>
   <si>
     <t>Macros</t>
-  </si>
-  <si>
-    <t>API.Revit</t>
   </si>
   <si>
     <t>Categoria Rvt</t>
@@ -2978,7 +2975,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3107,12 +3104,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBE79D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FFFFC7CE"/>
       </patternFill>
@@ -3218,7 +3209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3387,31 +3378,28 @@
     <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3430,17 +3418,95 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4067,7 +4133,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46268.699172916669</v>
+        <v>46269.535524537037</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>85</v>
@@ -4253,7 +4319,7 @@
         <v>57</v>
       </c>
       <c r="Y1" s="23" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="Z1" s="23" t="s">
         <v>885</v>
@@ -4268,7 +4334,7 @@
         <v>80</v>
       </c>
       <c r="AD1" s="23" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="2" spans="1:30" s="41" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4352,16 +4418,16 @@
         <f t="shared" ref="X2:X60" si="2">CONCATENATE("Key-FABR-",A2)</f>
         <v>Key-FABR-2</v>
       </c>
-      <c r="Y2" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z2" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB2" s="61" t="s">
+      <c r="Y2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="33" t="s">
@@ -4452,16 +4518,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-3</v>
       </c>
-      <c r="Y3" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z3" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA3" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB3" s="61" t="s">
+      <c r="Y3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB3" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="33" t="s">
@@ -4545,16 +4611,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-4</v>
       </c>
-      <c r="Y4" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z4" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA4" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB4" s="61" t="s">
+      <c r="Y4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB4" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="33" t="s">
@@ -4645,16 +4711,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-5</v>
       </c>
-      <c r="Y5" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z5" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB5" s="61" t="s">
+      <c r="Y5" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB5" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="33" t="s">
@@ -4745,16 +4811,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-6</v>
       </c>
-      <c r="Y6" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z6" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB6" s="61" t="s">
+      <c r="Y6" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB6" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="33" t="s">
@@ -4845,16 +4911,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-7</v>
       </c>
-      <c r="Y7" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z7" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA7" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB7" s="61" t="s">
+      <c r="Y7" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB7" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="33" t="s">
@@ -4945,16 +5011,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-8</v>
       </c>
-      <c r="Y8" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z8" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA8" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB8" s="61" t="s">
+      <c r="Y8" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z8" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA8" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB8" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="33" t="s">
@@ -5045,16 +5111,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-9</v>
       </c>
-      <c r="Y9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB9" s="61" t="s">
+      <c r="Y9" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z9" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB9" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="33" t="s">
@@ -5145,16 +5211,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-10</v>
       </c>
-      <c r="Y10" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z10" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA10" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB10" s="61" t="s">
+      <c r="Y10" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z10" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA10" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB10" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="33" t="s">
@@ -5245,16 +5311,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-11</v>
       </c>
-      <c r="Y11" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z11" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA11" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB11" s="61" t="s">
+      <c r="Y11" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z11" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA11" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB11" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="33" t="s">
@@ -5345,16 +5411,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-12</v>
       </c>
-      <c r="Y12" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z12" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA12" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB12" s="61" t="s">
+      <c r="Y12" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z12" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA12" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB12" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="33" t="s">
@@ -5438,16 +5504,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-13</v>
       </c>
-      <c r="Y13" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z13" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA13" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB13" s="61" t="s">
+      <c r="Y13" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z13" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA13" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB13" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC13" s="33" t="s">
@@ -5538,16 +5604,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-14</v>
       </c>
-      <c r="Y14" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z14" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA14" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB14" s="61" t="s">
+      <c r="Y14" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z14" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA14" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB14" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC14" s="33" t="s">
@@ -5638,16 +5704,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-15</v>
       </c>
-      <c r="Y15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB15" s="61" t="s">
+      <c r="Y15" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z15" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA15" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB15" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC15" s="33" t="s">
@@ -5738,16 +5804,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-16</v>
       </c>
-      <c r="Y16" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z16" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA16" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB16" s="61" t="s">
+      <c r="Y16" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z16" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA16" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB16" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC16" s="33" t="s">
@@ -5838,16 +5904,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-17</v>
       </c>
-      <c r="Y17" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z17" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA17" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB17" s="61" t="s">
+      <c r="Y17" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z17" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA17" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB17" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC17" s="33" t="s">
@@ -5938,16 +6004,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-18</v>
       </c>
-      <c r="Y18" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z18" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA18" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB18" s="61" t="s">
+      <c r="Y18" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z18" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA18" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB18" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC18" s="33" t="s">
@@ -6038,16 +6104,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-19</v>
       </c>
-      <c r="Y19" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z19" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA19" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB19" s="61" t="s">
+      <c r="Y19" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z19" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA19" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC19" s="33" t="s">
@@ -6138,16 +6204,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-20</v>
       </c>
-      <c r="Y20" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z20" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA20" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB20" s="61" t="s">
+      <c r="Y20" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z20" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA20" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB20" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC20" s="33" t="s">
@@ -6238,16 +6304,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-21</v>
       </c>
-      <c r="Y21" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z21" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA21" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB21" s="61" t="s">
+      <c r="Y21" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z21" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA21" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB21" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC21" s="33" t="s">
@@ -6331,16 +6397,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-22</v>
       </c>
-      <c r="Y22" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z22" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA22" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB22" s="61" t="s">
+      <c r="Y22" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z22" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA22" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB22" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC22" s="33" t="s">
@@ -6431,16 +6497,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-23</v>
       </c>
-      <c r="Y23" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z23" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA23" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB23" s="61" t="s">
+      <c r="Y23" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z23" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA23" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB23" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC23" s="33" t="s">
@@ -6531,16 +6597,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-24</v>
       </c>
-      <c r="Y24" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z24" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA24" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB24" s="61" t="s">
+      <c r="Y24" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z24" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA24" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB24" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC24" s="33" t="s">
@@ -6631,16 +6697,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-25</v>
       </c>
-      <c r="Y25" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z25" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA25" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB25" s="61" t="s">
+      <c r="Y25" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z25" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA25" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB25" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC25" s="33" t="s">
@@ -6731,16 +6797,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-26</v>
       </c>
-      <c r="Y26" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z26" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA26" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB26" s="61" t="s">
+      <c r="Y26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA26" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB26" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC26" s="33" t="s">
@@ -6831,16 +6897,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-27</v>
       </c>
-      <c r="Y27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB27" s="61" t="s">
+      <c r="Y27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA27" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB27" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC27" s="33" t="s">
@@ -6931,16 +6997,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-28</v>
       </c>
-      <c r="Y28" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z28" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA28" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB28" s="61" t="s">
+      <c r="Y28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB28" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC28" s="33" t="s">
@@ -7031,16 +7097,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-29</v>
       </c>
-      <c r="Y29" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z29" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA29" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB29" s="61" t="s">
+      <c r="Y29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA29" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB29" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC29" s="33" t="s">
@@ -7131,16 +7197,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-30</v>
       </c>
-      <c r="Y30" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z30" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA30" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB30" s="61" t="s">
+      <c r="Y30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA30" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB30" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC30" s="33" t="s">
@@ -7224,16 +7290,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-31</v>
       </c>
-      <c r="Y31" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z31" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA31" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB31" s="61" t="s">
+      <c r="Y31" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z31" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA31" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB31" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC31" s="33" t="s">
@@ -7324,16 +7390,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-32</v>
       </c>
-      <c r="Y32" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z32" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA32" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB32" s="61" t="s">
+      <c r="Y32" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z32" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA32" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB32" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC32" s="33" t="s">
@@ -7424,16 +7490,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-33</v>
       </c>
-      <c r="Y33" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z33" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA33" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB33" s="61" t="s">
+      <c r="Y33" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z33" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA33" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB33" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC33" s="33" t="s">
@@ -7524,16 +7590,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-34</v>
       </c>
-      <c r="Y34" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z34" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA34" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB34" s="61" t="s">
+      <c r="Y34" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z34" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA34" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB34" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC34" s="33" t="s">
@@ -7624,16 +7690,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-35</v>
       </c>
-      <c r="Y35" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z35" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA35" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB35" s="61" t="s">
+      <c r="Y35" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z35" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA35" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB35" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC35" s="33" t="s">
@@ -7724,16 +7790,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-36</v>
       </c>
-      <c r="Y36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB36" s="61" t="s">
+      <c r="Y36" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z36" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA36" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB36" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC36" s="33" t="s">
@@ -7824,16 +7890,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-37</v>
       </c>
-      <c r="Y37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB37" s="61" t="s">
+      <c r="Y37" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z37" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA37" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB37" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC37" s="33" t="s">
@@ -7924,16 +7990,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-38</v>
       </c>
-      <c r="Y38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB38" s="61" t="s">
+      <c r="Y38" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z38" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA38" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB38" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC38" s="33" t="s">
@@ -8024,16 +8090,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-39</v>
       </c>
-      <c r="Y39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB39" s="61" t="s">
+      <c r="Y39" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z39" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA39" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB39" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC39" s="33" t="s">
@@ -8117,16 +8183,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-40</v>
       </c>
-      <c r="Y40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB40" s="61" t="s">
+      <c r="Y40" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z40" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA40" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB40" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC40" s="33" t="s">
@@ -8217,16 +8283,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-41</v>
       </c>
-      <c r="Y41" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z41" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA41" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB41" s="61" t="s">
+      <c r="Y41" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z41" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA41" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB41" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC41" s="33" t="s">
@@ -8317,16 +8383,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-42</v>
       </c>
-      <c r="Y42" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z42" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA42" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB42" s="61" t="s">
+      <c r="Y42" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z42" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA42" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB42" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC42" s="33" t="s">
@@ -8417,16 +8483,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-43</v>
       </c>
-      <c r="Y43" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z43" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA43" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB43" s="61" t="s">
+      <c r="Y43" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z43" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA43" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB43" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC43" s="33" t="s">
@@ -8517,16 +8583,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-44</v>
       </c>
-      <c r="Y44" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z44" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA44" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB44" s="61" t="s">
+      <c r="Y44" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z44" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA44" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB44" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC44" s="33" t="s">
@@ -8617,16 +8683,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-45</v>
       </c>
-      <c r="Y45" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z45" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA45" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB45" s="61" t="s">
+      <c r="Y45" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z45" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA45" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB45" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC45" s="33" t="s">
@@ -8717,16 +8783,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-46</v>
       </c>
-      <c r="Y46" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z46" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA46" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB46" s="61" t="s">
+      <c r="Y46" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z46" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA46" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB46" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC46" s="33" t="s">
@@ -8817,16 +8883,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-47</v>
       </c>
-      <c r="Y47" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z47" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA47" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB47" s="61" t="s">
+      <c r="Y47" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z47" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA47" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB47" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC47" s="33" t="s">
@@ -8917,16 +8983,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-48</v>
       </c>
-      <c r="Y48" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z48" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA48" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB48" s="61" t="s">
+      <c r="Y48" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z48" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA48" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB48" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC48" s="33" t="s">
@@ -9010,16 +9076,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-49</v>
       </c>
-      <c r="Y49" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z49" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA49" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB49" s="61" t="s">
+      <c r="Y49" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z49" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA49" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB49" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC49" s="33" t="s">
@@ -9110,16 +9176,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-50</v>
       </c>
-      <c r="Y50" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z50" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA50" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB50" s="61" t="s">
+      <c r="Y50" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z50" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA50" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB50" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC50" s="33" t="s">
@@ -9210,16 +9276,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-51</v>
       </c>
-      <c r="Y51" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z51" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA51" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB51" s="61" t="s">
+      <c r="Y51" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z51" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA51" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB51" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC51" s="33" t="s">
@@ -9310,16 +9376,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-52</v>
       </c>
-      <c r="Y52" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z52" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA52" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB52" s="61" t="s">
+      <c r="Y52" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z52" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA52" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB52" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC52" s="33" t="s">
@@ -9410,16 +9476,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-53</v>
       </c>
-      <c r="Y53" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z53" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA53" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB53" s="61" t="s">
+      <c r="Y53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA53" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB53" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC53" s="33" t="s">
@@ -9510,16 +9576,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-54</v>
       </c>
-      <c r="Y54" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z54" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA54" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB54" s="61" t="s">
+      <c r="Y54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA54" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB54" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC54" s="33" t="s">
@@ -9610,16 +9676,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-55</v>
       </c>
-      <c r="Y55" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z55" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA55" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB55" s="61" t="s">
+      <c r="Y55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA55" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB55" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC55" s="33" t="s">
@@ -9710,16 +9776,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-56</v>
       </c>
-      <c r="Y56" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z56" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA56" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB56" s="61" t="s">
+      <c r="Y56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA56" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB56" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC56" s="33" t="s">
@@ -9810,16 +9876,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-57</v>
       </c>
-      <c r="Y57" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z57" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA57" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB57" s="61" t="s">
+      <c r="Y57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA57" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB57" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC57" s="33" t="s">
@@ -9903,16 +9969,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-58</v>
       </c>
-      <c r="Y58" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z58" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA58" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB58" s="61" t="s">
+      <c r="Y58" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z58" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA58" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB58" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC58" s="33" t="s">
@@ -10003,16 +10069,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-59</v>
       </c>
-      <c r="Y59" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z59" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA59" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB59" s="61" t="s">
+      <c r="Y59" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z59" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA59" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB59" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC59" s="33" t="s">
@@ -10103,16 +10169,16 @@
         <f t="shared" si="2"/>
         <v>Key-FABR-60</v>
       </c>
-      <c r="Y60" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z60" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA60" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB60" s="61" t="s">
+      <c r="Y60" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z60" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA60" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB60" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC60" s="33" t="s">
@@ -10203,16 +10269,16 @@
         <f t="shared" ref="X61:X124" si="24">CONCATENATE("Key-FABR-",A61)</f>
         <v>Key-FABR-61</v>
       </c>
-      <c r="Y61" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z61" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA61" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB61" s="61" t="s">
+      <c r="Y61" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z61" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA61" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB61" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC61" s="33" t="s">
@@ -10303,16 +10369,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-62</v>
       </c>
-      <c r="Y62" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z62" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA62" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB62" s="61" t="s">
+      <c r="Y62" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z62" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA62" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB62" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC62" s="33" t="s">
@@ -10403,16 +10469,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-63</v>
       </c>
-      <c r="Y63" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z63" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA63" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB63" s="61" t="s">
+      <c r="Y63" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z63" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA63" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB63" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC63" s="33" t="s">
@@ -10503,16 +10569,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-64</v>
       </c>
-      <c r="Y64" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z64" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA64" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB64" s="61" t="s">
+      <c r="Y64" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z64" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA64" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB64" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC64" s="33" t="s">
@@ -10603,16 +10669,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-65</v>
       </c>
-      <c r="Y65" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z65" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA65" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB65" s="61" t="s">
+      <c r="Y65" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z65" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA65" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB65" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC65" s="33" t="s">
@@ -10703,16 +10769,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-66</v>
       </c>
-      <c r="Y66" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z66" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA66" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB66" s="61" t="s">
+      <c r="Y66" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z66" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA66" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB66" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC66" s="33" t="s">
@@ -10796,16 +10862,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-67</v>
       </c>
-      <c r="Y67" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z67" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA67" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB67" s="61" t="s">
+      <c r="Y67" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z67" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA67" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB67" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC67" s="33" t="s">
@@ -10896,16 +10962,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-68</v>
       </c>
-      <c r="Y68" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z68" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA68" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB68" s="61" t="s">
+      <c r="Y68" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z68" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA68" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB68" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC68" s="33" t="s">
@@ -10996,16 +11062,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-69</v>
       </c>
-      <c r="Y69" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z69" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA69" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB69" s="61" t="s">
+      <c r="Y69" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z69" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA69" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB69" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC69" s="33" t="s">
@@ -11096,16 +11162,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-70</v>
       </c>
-      <c r="Y70" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z70" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA70" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB70" s="61" t="s">
+      <c r="Y70" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z70" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA70" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB70" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC70" s="33" t="s">
@@ -11196,16 +11262,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-71</v>
       </c>
-      <c r="Y71" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z71" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA71" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB71" s="61" t="s">
+      <c r="Y71" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z71" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA71" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB71" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC71" s="33" t="s">
@@ -11296,16 +11362,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-72</v>
       </c>
-      <c r="Y72" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z72" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA72" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB72" s="61" t="s">
+      <c r="Y72" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z72" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA72" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB72" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC72" s="33" t="s">
@@ -11396,16 +11462,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-73</v>
       </c>
-      <c r="Y73" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z73" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA73" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB73" s="61" t="s">
+      <c r="Y73" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z73" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA73" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB73" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC73" s="33" t="s">
@@ -11496,16 +11562,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-74</v>
       </c>
-      <c r="Y74" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z74" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA74" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB74" s="61" t="s">
+      <c r="Y74" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z74" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA74" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB74" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC74" s="33" t="s">
@@ -11596,16 +11662,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-75</v>
       </c>
-      <c r="Y75" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z75" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA75" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB75" s="61" t="s">
+      <c r="Y75" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z75" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA75" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB75" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC75" s="33" t="s">
@@ -11689,16 +11755,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-76</v>
       </c>
-      <c r="Y76" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z76" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA76" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB76" s="61" t="s">
+      <c r="Y76" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z76" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA76" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB76" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC76" s="33" t="s">
@@ -11789,16 +11855,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-77</v>
       </c>
-      <c r="Y77" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z77" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA77" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB77" s="61" t="s">
+      <c r="Y77" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z77" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA77" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB77" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC77" s="33" t="s">
@@ -11889,16 +11955,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-78</v>
       </c>
-      <c r="Y78" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z78" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA78" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB78" s="61" t="s">
+      <c r="Y78" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z78" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA78" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB78" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC78" s="33" t="s">
@@ -11989,16 +12055,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-79</v>
       </c>
-      <c r="Y79" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z79" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA79" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB79" s="61" t="s">
+      <c r="Y79" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z79" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA79" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB79" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC79" s="33" t="s">
@@ -12089,16 +12155,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-80</v>
       </c>
-      <c r="Y80" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z80" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA80" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB80" s="61" t="s">
+      <c r="Y80" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z80" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA80" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB80" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC80" s="33" t="s">
@@ -12189,16 +12255,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-81</v>
       </c>
-      <c r="Y81" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z81" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA81" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB81" s="61" t="s">
+      <c r="Y81" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z81" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA81" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB81" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC81" s="33" t="s">
@@ -12289,16 +12355,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-82</v>
       </c>
-      <c r="Y82" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z82" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA82" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB82" s="61" t="s">
+      <c r="Y82" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z82" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA82" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB82" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC82" s="33" t="s">
@@ -12389,16 +12455,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-83</v>
       </c>
-      <c r="Y83" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z83" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA83" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB83" s="61" t="s">
+      <c r="Y83" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z83" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA83" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB83" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC83" s="33" t="s">
@@ -12489,16 +12555,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-84</v>
       </c>
-      <c r="Y84" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z84" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA84" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB84" s="61" t="s">
+      <c r="Y84" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z84" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA84" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB84" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC84" s="33" t="s">
@@ -12582,16 +12648,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-85</v>
       </c>
-      <c r="Y85" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z85" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA85" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB85" s="61" t="s">
+      <c r="Y85" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z85" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA85" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB85" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC85" s="33" t="s">
@@ -12682,16 +12748,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-86</v>
       </c>
-      <c r="Y86" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z86" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA86" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB86" s="61" t="s">
+      <c r="Y86" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z86" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA86" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB86" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC86" s="33" t="s">
@@ -12782,16 +12848,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-87</v>
       </c>
-      <c r="Y87" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z87" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA87" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB87" s="61" t="s">
+      <c r="Y87" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z87" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA87" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB87" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC87" s="33" t="s">
@@ -12882,16 +12948,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-88</v>
       </c>
-      <c r="Y88" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z88" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA88" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB88" s="61" t="s">
+      <c r="Y88" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z88" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA88" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB88" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC88" s="33" t="s">
@@ -12982,16 +13048,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-89</v>
       </c>
-      <c r="Y89" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z89" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA89" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB89" s="61" t="s">
+      <c r="Y89" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z89" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA89" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB89" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC89" s="33" t="s">
@@ -13082,16 +13148,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-90</v>
       </c>
-      <c r="Y90" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z90" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA90" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB90" s="61" t="s">
+      <c r="Y90" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z90" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA90" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB90" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC90" s="33" t="s">
@@ -13182,16 +13248,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-91</v>
       </c>
-      <c r="Y91" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z91" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA91" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB91" s="61" t="s">
+      <c r="Y91" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z91" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA91" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB91" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC91" s="33" t="s">
@@ -13282,16 +13348,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-92</v>
       </c>
-      <c r="Y92" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z92" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA92" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB92" s="61" t="s">
+      <c r="Y92" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z92" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA92" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB92" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC92" s="33" t="s">
@@ -13382,16 +13448,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-93</v>
       </c>
-      <c r="Y93" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z93" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA93" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB93" s="61" t="s">
+      <c r="Y93" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z93" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA93" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB93" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC93" s="33" t="s">
@@ -13475,16 +13541,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-94</v>
       </c>
-      <c r="Y94" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z94" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA94" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB94" s="61" t="s">
+      <c r="Y94" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z94" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA94" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB94" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC94" s="33" t="s">
@@ -13575,16 +13641,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-95</v>
       </c>
-      <c r="Y95" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z95" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA95" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB95" s="61" t="s">
+      <c r="Y95" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z95" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA95" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB95" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC95" s="33" t="s">
@@ -13675,16 +13741,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-96</v>
       </c>
-      <c r="Y96" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z96" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA96" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB96" s="61" t="s">
+      <c r="Y96" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z96" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA96" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB96" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC96" s="33" t="s">
@@ -13775,16 +13841,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-97</v>
       </c>
-      <c r="Y97" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z97" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA97" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB97" s="61" t="s">
+      <c r="Y97" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z97" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA97" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB97" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC97" s="33" t="s">
@@ -13875,16 +13941,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-98</v>
       </c>
-      <c r="Y98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA98" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB98" s="61" t="s">
+      <c r="Y98" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z98" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA98" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB98" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC98" s="33" t="s">
@@ -13975,16 +14041,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-99</v>
       </c>
-      <c r="Y99" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z99" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA99" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB99" s="61" t="s">
+      <c r="Y99" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z99" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA99" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB99" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC99" s="33" t="s">
@@ -14075,16 +14141,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-100</v>
       </c>
-      <c r="Y100" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z100" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA100" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB100" s="61" t="s">
+      <c r="Y100" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z100" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA100" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB100" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC100" s="33" t="s">
@@ -14175,16 +14241,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-101</v>
       </c>
-      <c r="Y101" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z101" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA101" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB101" s="61" t="s">
+      <c r="Y101" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z101" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA101" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB101" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC101" s="33" t="s">
@@ -14275,16 +14341,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-102</v>
       </c>
-      <c r="Y102" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z102" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA102" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB102" s="61" t="s">
+      <c r="Y102" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z102" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA102" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB102" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC102" s="33" t="s">
@@ -14368,16 +14434,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-103</v>
       </c>
-      <c r="Y103" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z103" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA103" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB103" s="61" t="s">
+      <c r="Y103" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z103" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA103" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB103" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC103" s="33" t="s">
@@ -14468,16 +14534,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-104</v>
       </c>
-      <c r="Y104" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z104" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA104" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB104" s="61" t="s">
+      <c r="Y104" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z104" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA104" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB104" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC104" s="33" t="s">
@@ -14568,16 +14634,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-105</v>
       </c>
-      <c r="Y105" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z105" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA105" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB105" s="61" t="s">
+      <c r="Y105" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z105" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA105" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB105" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC105" s="33" t="s">
@@ -14668,16 +14734,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-106</v>
       </c>
-      <c r="Y106" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z106" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA106" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB106" s="61" t="s">
+      <c r="Y106" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z106" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA106" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB106" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC106" s="33" t="s">
@@ -14768,16 +14834,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-107</v>
       </c>
-      <c r="Y107" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z107" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA107" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB107" s="61" t="s">
+      <c r="Y107" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z107" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA107" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB107" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC107" s="33" t="s">
@@ -14868,16 +14934,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-108</v>
       </c>
-      <c r="Y108" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z108" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA108" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB108" s="61" t="s">
+      <c r="Y108" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z108" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA108" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB108" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC108" s="33" t="s">
@@ -14968,16 +15034,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-109</v>
       </c>
-      <c r="Y109" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z109" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA109" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB109" s="61" t="s">
+      <c r="Y109" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z109" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA109" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB109" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC109" s="33" t="s">
@@ -15068,16 +15134,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-110</v>
       </c>
-      <c r="Y110" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z110" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA110" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB110" s="61" t="s">
+      <c r="Y110" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z110" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA110" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB110" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC110" s="33" t="s">
@@ -15168,16 +15234,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-111</v>
       </c>
-      <c r="Y111" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z111" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA111" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB111" s="61" t="s">
+      <c r="Y111" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z111" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA111" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB111" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC111" s="33" t="s">
@@ -15261,16 +15327,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-112</v>
       </c>
-      <c r="Y112" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z112" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA112" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB112" s="61" t="s">
+      <c r="Y112" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z112" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA112" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB112" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC112" s="33" t="s">
@@ -15361,16 +15427,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-113</v>
       </c>
-      <c r="Y113" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z113" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA113" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB113" s="61" t="s">
+      <c r="Y113" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z113" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA113" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB113" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC113" s="33" t="s">
@@ -15461,16 +15527,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-114</v>
       </c>
-      <c r="Y114" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z114" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA114" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB114" s="61" t="s">
+      <c r="Y114" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z114" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA114" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB114" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC114" s="33" t="s">
@@ -15561,16 +15627,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-115</v>
       </c>
-      <c r="Y115" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z115" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA115" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB115" s="61" t="s">
+      <c r="Y115" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z115" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA115" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB115" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC115" s="33" t="s">
@@ -15661,16 +15727,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-116</v>
       </c>
-      <c r="Y116" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z116" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA116" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB116" s="61" t="s">
+      <c r="Y116" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z116" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA116" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB116" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC116" s="33" t="s">
@@ -15761,16 +15827,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-117</v>
       </c>
-      <c r="Y117" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z117" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA117" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB117" s="61" t="s">
+      <c r="Y117" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z117" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA117" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB117" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC117" s="33" t="s">
@@ -15861,16 +15927,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-118</v>
       </c>
-      <c r="Y118" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z118" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA118" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB118" s="61" t="s">
+      <c r="Y118" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z118" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA118" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB118" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC118" s="33" t="s">
@@ -15961,16 +16027,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-119</v>
       </c>
-      <c r="Y119" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z119" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA119" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB119" s="61" t="s">
+      <c r="Y119" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z119" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA119" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB119" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC119" s="54" t="s">
@@ -16061,16 +16127,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-120</v>
       </c>
-      <c r="Y120" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z120" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA120" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB120" s="61" t="s">
+      <c r="Y120" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z120" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA120" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB120" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC120" s="54" t="s">
@@ -16161,16 +16227,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-121</v>
       </c>
-      <c r="Y121" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z121" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA121" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB121" s="61" t="s">
+      <c r="Y121" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z121" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA121" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB121" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC121" s="54" t="s">
@@ -16261,16 +16327,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-122</v>
       </c>
-      <c r="Y122" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z122" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA122" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB122" s="61" t="s">
+      <c r="Y122" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z122" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA122" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB122" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC122" s="54" t="s">
@@ -16361,16 +16427,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-123</v>
       </c>
-      <c r="Y123" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z123" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA123" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB123" s="61" t="s">
+      <c r="Y123" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z123" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA123" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB123" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC123" s="54" t="s">
@@ -16461,16 +16527,16 @@
         <f t="shared" si="24"/>
         <v>Key-FABR-124</v>
       </c>
-      <c r="Y124" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z124" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA124" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB124" s="61" t="s">
+      <c r="Y124" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z124" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA124" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB124" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC124" s="54" t="s">
@@ -16561,16 +16627,16 @@
         <f t="shared" ref="X125:X149" si="47">CONCATENATE("Key-FABR-",A125)</f>
         <v>Key-FABR-125</v>
       </c>
-      <c r="Y125" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z125" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA125" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB125" s="61" t="s">
+      <c r="Y125" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z125" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA125" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB125" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC125" s="54" t="s">
@@ -16661,16 +16727,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-126</v>
       </c>
-      <c r="Y126" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z126" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA126" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB126" s="61" t="s">
+      <c r="Y126" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z126" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA126" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB126" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC126" s="54" t="s">
@@ -16761,16 +16827,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-127</v>
       </c>
-      <c r="Y127" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z127" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA127" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB127" s="61" t="s">
+      <c r="Y127" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z127" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA127" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB127" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC127" s="54" t="s">
@@ -16861,16 +16927,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-128</v>
       </c>
-      <c r="Y128" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z128" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA128" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB128" s="61" t="s">
+      <c r="Y128" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z128" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA128" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB128" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC128" s="54" t="s">
@@ -16961,16 +17027,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-129</v>
       </c>
-      <c r="Y129" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z129" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA129" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB129" s="61" t="s">
+      <c r="Y129" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z129" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA129" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB129" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC129" s="54" t="s">
@@ -17061,16 +17127,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-130</v>
       </c>
-      <c r="Y130" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z130" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA130" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB130" s="61" t="s">
+      <c r="Y130" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z130" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA130" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB130" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC130" s="54" t="s">
@@ -17161,16 +17227,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-131</v>
       </c>
-      <c r="Y131" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z131" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA131" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB131" s="61" t="s">
+      <c r="Y131" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z131" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA131" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB131" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC131" s="54" t="s">
@@ -17261,16 +17327,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-132</v>
       </c>
-      <c r="Y132" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z132" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA132" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB132" s="61" t="s">
+      <c r="Y132" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z132" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA132" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB132" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC132" s="54" t="s">
@@ -17361,16 +17427,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-133</v>
       </c>
-      <c r="Y133" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z133" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA133" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB133" s="61" t="s">
+      <c r="Y133" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z133" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA133" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB133" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC133" s="54" t="s">
@@ -17461,16 +17527,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-134</v>
       </c>
-      <c r="Y134" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z134" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA134" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB134" s="61" t="s">
+      <c r="Y134" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z134" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA134" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB134" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC134" s="54" t="s">
@@ -17561,16 +17627,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-135</v>
       </c>
-      <c r="Y135" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z135" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA135" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB135" s="61" t="s">
+      <c r="Y135" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z135" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA135" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB135" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC135" s="54" t="s">
@@ -17661,16 +17727,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-136</v>
       </c>
-      <c r="Y136" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z136" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA136" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB136" s="61" t="s">
+      <c r="Y136" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z136" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA136" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB136" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC136" s="54" t="s">
@@ -17761,16 +17827,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-137</v>
       </c>
-      <c r="Y137" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z137" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA137" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB137" s="61" t="s">
+      <c r="Y137" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z137" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA137" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB137" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC137" s="54" t="s">
@@ -17861,16 +17927,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-138</v>
       </c>
-      <c r="Y138" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z138" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA138" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB138" s="61" t="s">
+      <c r="Y138" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z138" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA138" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB138" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC138" s="54" t="s">
@@ -17961,16 +18027,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-139</v>
       </c>
-      <c r="Y139" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z139" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA139" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB139" s="61" t="s">
+      <c r="Y139" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z139" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA139" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB139" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC139" s="54" t="s">
@@ -18061,16 +18127,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-140</v>
       </c>
-      <c r="Y140" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z140" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA140" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB140" s="61" t="s">
+      <c r="Y140" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z140" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA140" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB140" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC140" s="54" t="s">
@@ -18161,16 +18227,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-141</v>
       </c>
-      <c r="Y141" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z141" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA141" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB141" s="61" t="s">
+      <c r="Y141" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z141" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA141" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB141" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC141" s="54" t="s">
@@ -18261,16 +18327,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-142</v>
       </c>
-      <c r="Y142" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z142" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA142" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB142" s="61" t="s">
+      <c r="Y142" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z142" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA142" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB142" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC142" s="54" t="s">
@@ -18361,16 +18427,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-143</v>
       </c>
-      <c r="Y143" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z143" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA143" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB143" s="61" t="s">
+      <c r="Y143" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z143" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA143" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB143" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC143" s="54" t="s">
@@ -18461,16 +18527,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-144</v>
       </c>
-      <c r="Y144" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z144" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA144" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB144" s="61" t="s">
+      <c r="Y144" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z144" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA144" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB144" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC144" s="54" t="s">
@@ -18561,16 +18627,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-145</v>
       </c>
-      <c r="Y145" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z145" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA145" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB145" s="61" t="s">
+      <c r="Y145" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z145" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA145" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB145" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC145" s="54" t="s">
@@ -18661,16 +18727,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-146</v>
       </c>
-      <c r="Y146" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z146" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA146" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB146" s="61" t="s">
+      <c r="Y146" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z146" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA146" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB146" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC146" s="54" t="s">
@@ -18761,16 +18827,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-147</v>
       </c>
-      <c r="Y147" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z147" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA147" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB147" s="61" t="s">
+      <c r="Y147" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z147" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA147" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB147" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC147" s="54" t="s">
@@ -18861,16 +18927,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-148</v>
       </c>
-      <c r="Y148" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z148" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA148" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB148" s="61" t="s">
+      <c r="Y148" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z148" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA148" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB148" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC148" s="54" t="s">
@@ -18961,16 +19027,16 @@
         <f t="shared" si="47"/>
         <v>Key-FABR-149</v>
       </c>
-      <c r="Y149" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z149" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA149" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB149" s="61" t="s">
+      <c r="Y149" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z149" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA149" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB149" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AC149" s="54" t="s">
@@ -18980,24 +19046,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:30" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="48">
         <v>150</v>
       </c>
-      <c r="B150" s="73" t="s">
+      <c r="B150" s="72" t="s">
         <v>858</v>
       </c>
-      <c r="C150" s="74" t="s">
+      <c r="C150" s="73" t="s">
         <v>888</v>
       </c>
-      <c r="D150" s="74" t="s">
+      <c r="D150" s="73" t="s">
         <v>890</v>
       </c>
-      <c r="E150" s="74" t="s">
+      <c r="E150" s="73" t="s">
         <v>889</v>
       </c>
-      <c r="F150" s="74" t="s">
-        <v>916</v>
+      <c r="F150" s="73" t="s">
+        <v>915</v>
       </c>
       <c r="G150" s="52" t="s">
         <v>9</v>
@@ -19014,30 +19080,30 @@
       <c r="K150" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="L150" s="59" t="str">
+      <c r="L150" s="58" t="str">
         <f t="shared" ref="L150:O154" si="62">SUBSTITUTE(CONCATENATE("", C150), ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="M150" s="59" t="str">
+      <c r="M150" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Macros</v>
       </c>
-      <c r="N150" s="59" t="str">
+      <c r="N150" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Métodos</v>
       </c>
-      <c r="O150" s="59" t="str">
+      <c r="O150" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Função Auxiliar</v>
       </c>
       <c r="P150" s="33" t="s">
+        <v>916</v>
+      </c>
+      <c r="Q150" s="33" t="s">
         <v>917</v>
       </c>
-      <c r="Q150" s="33" t="s">
+      <c r="R150" s="33" t="s">
         <v>918</v>
-      </c>
-      <c r="R150" s="33" t="s">
-        <v>919</v>
       </c>
       <c r="S150" s="33" t="s">
         <v>9</v>
@@ -19050,7 +19116,7 @@
         <f t="shared" si="59"/>
         <v>Macros</v>
       </c>
-      <c r="V150" s="60" t="str">
+      <c r="V150" s="59" t="str">
         <f t="shared" si="59"/>
         <v>Métodos</v>
       </c>
@@ -19061,43 +19127,43 @@
         <f t="shared" ref="X150:X154" si="63">CONCATENATE("Key-FABR-",A150)</f>
         <v>Key-FABR-150</v>
       </c>
-      <c r="Y150" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z150" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA150" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB150" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC150" s="61" t="s">
+      <c r="Y150" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z150" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA150" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB150" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC150" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AD150" s="33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:30" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="48">
         <v>151</v>
       </c>
-      <c r="B151" s="73" t="s">
+      <c r="B151" s="72" t="s">
         <v>858</v>
       </c>
-      <c r="C151" s="74" t="s">
+      <c r="C151" s="73" t="s">
         <v>888</v>
       </c>
-      <c r="D151" s="74" t="s">
+      <c r="D151" s="73" t="s">
         <v>890</v>
       </c>
-      <c r="E151" s="74" t="s">
+      <c r="E151" s="73" t="s">
         <v>889</v>
       </c>
-      <c r="F151" s="74" t="s">
-        <v>920</v>
+      <c r="F151" s="73" t="s">
+        <v>919</v>
       </c>
       <c r="G151" s="52" t="s">
         <v>9</v>
@@ -19114,30 +19180,30 @@
       <c r="K151" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="L151" s="59" t="str">
+      <c r="L151" s="58" t="str">
         <f t="shared" si="62"/>
         <v>De API</v>
       </c>
-      <c r="M151" s="59" t="str">
+      <c r="M151" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Macros</v>
       </c>
-      <c r="N151" s="59" t="str">
+      <c r="N151" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Métodos</v>
       </c>
-      <c r="O151" s="59" t="str">
+      <c r="O151" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Função Global</v>
       </c>
       <c r="P151" s="33" t="s">
+        <v>920</v>
+      </c>
+      <c r="Q151" s="33" t="s">
         <v>921</v>
       </c>
-      <c r="Q151" s="33" t="s">
+      <c r="R151" s="33" t="s">
         <v>922</v>
-      </c>
-      <c r="R151" s="33" t="s">
-        <v>923</v>
       </c>
       <c r="S151" s="33" t="s">
         <v>9</v>
@@ -19150,7 +19216,7 @@
         <f t="shared" si="59"/>
         <v>Macros</v>
       </c>
-      <c r="V151" s="60" t="str">
+      <c r="V151" s="59" t="str">
         <f t="shared" si="59"/>
         <v>Métodos</v>
       </c>
@@ -19161,43 +19227,43 @@
         <f t="shared" si="63"/>
         <v>Key-FABR-151</v>
       </c>
-      <c r="Y151" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z151" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA151" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB151" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC151" s="61" t="s">
+      <c r="Y151" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z151" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA151" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB151" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC151" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AD151" s="33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:30" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="48">
         <v>152</v>
       </c>
-      <c r="B152" s="73" t="s">
+      <c r="B152" s="72" t="s">
         <v>858</v>
       </c>
-      <c r="C152" s="74" t="s">
+      <c r="C152" s="73" t="s">
         <v>888</v>
       </c>
-      <c r="D152" s="74" t="s">
+      <c r="D152" s="73" t="s">
         <v>890</v>
       </c>
-      <c r="E152" s="74" t="s">
+      <c r="E152" s="73" t="s">
         <v>889</v>
       </c>
-      <c r="F152" s="74" t="s">
-        <v>924</v>
+      <c r="F152" s="73" t="s">
+        <v>923</v>
       </c>
       <c r="G152" s="52" t="s">
         <v>9</v>
@@ -19214,30 +19280,30 @@
       <c r="K152" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="L152" s="59" t="str">
+      <c r="L152" s="58" t="str">
         <f t="shared" si="62"/>
         <v>De API</v>
       </c>
-      <c r="M152" s="59" t="str">
+      <c r="M152" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Macros</v>
       </c>
-      <c r="N152" s="59" t="str">
+      <c r="N152" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Métodos</v>
       </c>
-      <c r="O152" s="59" t="str">
+      <c r="O152" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Função Local</v>
       </c>
       <c r="P152" s="33" t="s">
+        <v>924</v>
+      </c>
+      <c r="Q152" s="33" t="s">
         <v>925</v>
       </c>
-      <c r="Q152" s="33" t="s">
+      <c r="R152" s="33" t="s">
         <v>926</v>
-      </c>
-      <c r="R152" s="33" t="s">
-        <v>927</v>
       </c>
       <c r="S152" s="33" t="s">
         <v>9</v>
@@ -19250,7 +19316,7 @@
         <f t="shared" si="59"/>
         <v>Macros</v>
       </c>
-      <c r="V152" s="60" t="str">
+      <c r="V152" s="59" t="str">
         <f t="shared" si="59"/>
         <v>Métodos</v>
       </c>
@@ -19261,43 +19327,43 @@
         <f t="shared" si="63"/>
         <v>Key-FABR-152</v>
       </c>
-      <c r="Y152" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z152" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA152" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB152" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC152" s="61" t="s">
+      <c r="Y152" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z152" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA152" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB152" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC152" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AD152" s="33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:30" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="48">
         <v>153</v>
       </c>
-      <c r="B153" s="73" t="s">
+      <c r="B153" s="72" t="s">
         <v>858</v>
       </c>
-      <c r="C153" s="74" t="s">
+      <c r="C153" s="73" t="s">
         <v>888</v>
       </c>
-      <c r="D153" s="74" t="s">
+      <c r="D153" s="73" t="s">
         <v>890</v>
       </c>
-      <c r="E153" s="74" t="s">
+      <c r="E153" s="73" t="s">
         <v>889</v>
       </c>
-      <c r="F153" s="74" t="s">
-        <v>928</v>
+      <c r="F153" s="73" t="s">
+        <v>927</v>
       </c>
       <c r="G153" s="52" t="s">
         <v>9</v>
@@ -19314,30 +19380,30 @@
       <c r="K153" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="L153" s="59" t="str">
+      <c r="L153" s="58" t="str">
         <f t="shared" si="62"/>
         <v>De API</v>
       </c>
-      <c r="M153" s="59" t="str">
+      <c r="M153" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Macros</v>
       </c>
-      <c r="N153" s="59" t="str">
+      <c r="N153" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Métodos</v>
       </c>
-      <c r="O153" s="59" t="str">
+      <c r="O153" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Função Filtro</v>
       </c>
       <c r="P153" s="33" t="s">
+        <v>928</v>
+      </c>
+      <c r="Q153" s="33" t="s">
         <v>929</v>
       </c>
-      <c r="Q153" s="33" t="s">
+      <c r="R153" s="33" t="s">
         <v>930</v>
-      </c>
-      <c r="R153" s="33" t="s">
-        <v>931</v>
       </c>
       <c r="S153" s="33" t="s">
         <v>9</v>
@@ -19350,7 +19416,7 @@
         <f t="shared" si="59"/>
         <v>Macros</v>
       </c>
-      <c r="V153" s="60" t="str">
+      <c r="V153" s="59" t="str">
         <f t="shared" si="59"/>
         <v>Métodos</v>
       </c>
@@ -19361,44 +19427,44 @@
         <f t="shared" si="63"/>
         <v>Key-FABR-153</v>
       </c>
-      <c r="Y153" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z153" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA153" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB153" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC153" s="61" t="s">
+      <c r="Y153" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z153" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA153" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB153" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC153" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AD153" s="33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:30" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="48">
         <v>154</v>
       </c>
-      <c r="B154" s="73" t="s">
+      <c r="B154" s="72" t="s">
         <v>858</v>
       </c>
-      <c r="C154" s="74" t="s">
+      <c r="C154" s="73" t="s">
         <v>888</v>
       </c>
-      <c r="D154" s="74" t="s">
+      <c r="D154" s="73" t="s">
         <v>890</v>
       </c>
-      <c r="E154" s="74" t="s">
+      <c r="E154" s="73" t="s">
+        <v>931</v>
+      </c>
+      <c r="F154" s="73" t="s">
         <v>932</v>
       </c>
-      <c r="F154" s="74" t="s">
-        <v>933</v>
-      </c>
       <c r="G154" s="52" t="s">
         <v>9</v>
       </c>
@@ -19414,30 +19480,30 @@
       <c r="K154" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="L154" s="59" t="str">
+      <c r="L154" s="58" t="str">
         <f t="shared" si="62"/>
         <v>De API</v>
       </c>
-      <c r="M154" s="59" t="str">
+      <c r="M154" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Macros</v>
       </c>
-      <c r="N154" s="59" t="str">
+      <c r="N154" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Códigos Visuais</v>
       </c>
-      <c r="O154" s="59" t="str">
+      <c r="O154" s="58" t="str">
         <f t="shared" si="62"/>
         <v>Bloco de Código</v>
       </c>
       <c r="P154" s="33" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q154" s="33" t="s">
         <v>934</v>
       </c>
-      <c r="Q154" s="33" t="s">
+      <c r="R154" s="33" t="s">
         <v>935</v>
-      </c>
-      <c r="R154" s="33" t="s">
-        <v>936</v>
       </c>
       <c r="S154" s="33" t="s">
         <v>9</v>
@@ -19450,7 +19516,7 @@
         <f t="shared" si="59"/>
         <v>Macros</v>
       </c>
-      <c r="V154" s="60" t="str">
+      <c r="V154" s="59" t="str">
         <f t="shared" si="59"/>
         <v>Códigos Visuais</v>
       </c>
@@ -19461,19 +19527,19 @@
         <f t="shared" si="63"/>
         <v>Key-FABR-154</v>
       </c>
-      <c r="Y154" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z154" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA154" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB154" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC154" s="61" t="s">
+      <c r="Y154" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z154" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA154" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB154" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC154" s="60" t="s">
         <v>9</v>
       </c>
       <c r="AD154" s="33" t="s">
@@ -19486,19 +19552,19 @@
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="A2:B154">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E154:F154">
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F150:F153">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F1048576 F1:F149">
-    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -19877,70 +19943,70 @@
       <c r="M2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="71" t="s">
+      <c r="N2" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="71" t="s">
+      <c r="P2" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="71" t="s">
+      <c r="R2" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="71" t="s">
+      <c r="T2" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V2" s="71" t="s">
+      <c r="V2" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X2" s="71" t="s">
+      <c r="X2" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB2" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC2" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD2" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE2" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF2" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG2" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH2" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI2" s="72" t="s">
+      <c r="Z2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG2" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH2" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI2" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -19984,70 +20050,70 @@
       <c r="M3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="71" t="s">
+      <c r="N3" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="71" t="s">
+      <c r="P3" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="71" t="s">
+      <c r="R3" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="71" t="s">
+      <c r="T3" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="71" t="s">
+      <c r="V3" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X3" s="71" t="s">
+      <c r="X3" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA3" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB3" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC3" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD3" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE3" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF3" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG3" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH3" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI3" s="72" t="s">
+      <c r="Z3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE3" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH3" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI3" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -20091,70 +20157,70 @@
       <c r="M4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="71" t="s">
+      <c r="N4" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="71" t="s">
+      <c r="P4" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R4" s="71" t="s">
+      <c r="R4" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="71" t="s">
+      <c r="T4" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V4" s="71" t="s">
+      <c r="V4" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X4" s="71" t="s">
+      <c r="X4" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z4" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA4" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB4" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC4" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD4" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE4" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF4" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG4" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH4" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI4" s="72" t="s">
+      <c r="Z4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC4" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE4" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG4" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH4" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI4" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -20198,70 +20264,70 @@
       <c r="M5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="71" t="s">
+      <c r="N5" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="71" t="s">
+      <c r="P5" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R5" s="71" t="s">
+      <c r="R5" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="71" t="s">
+      <c r="T5" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V5" s="71" t="s">
+      <c r="V5" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X5" s="71" t="s">
+      <c r="X5" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z5" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB5" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC5" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD5" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE5" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF5" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG5" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH5" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI5" s="72" t="s">
+      <c r="Z5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE5" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG5" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH5" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI5" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -20305,70 +20371,70 @@
       <c r="M6" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N6" s="71" t="s">
+      <c r="N6" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="71" t="s">
+      <c r="P6" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R6" s="71" t="s">
+      <c r="R6" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T6" s="71" t="s">
+      <c r="T6" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V6" s="71" t="s">
+      <c r="V6" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X6" s="71" t="s">
+      <c r="X6" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB6" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC6" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD6" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE6" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF6" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG6" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH6" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI6" s="72" t="s">
+      <c r="Z6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE6" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG6" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH6" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI6" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -20412,70 +20478,70 @@
       <c r="M7" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N7" s="71" t="s">
+      <c r="N7" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="71" t="s">
+      <c r="P7" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R7" s="71" t="s">
+      <c r="R7" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T7" s="71" t="s">
+      <c r="T7" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V7" s="71" t="s">
+      <c r="V7" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X7" s="71" t="s">
+      <c r="X7" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z7" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA7" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB7" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC7" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD7" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE7" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF7" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG7" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH7" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI7" s="72" t="s">
+      <c r="Z7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE7" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG7" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH7" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI7" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -20519,70 +20585,70 @@
       <c r="M8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N8" s="71" t="s">
+      <c r="N8" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P8" s="71" t="s">
+      <c r="P8" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R8" s="71" t="s">
+      <c r="R8" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="71" t="s">
+      <c r="T8" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V8" s="71" t="s">
+      <c r="V8" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X8" s="71" t="s">
+      <c r="X8" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y8" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z8" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA8" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB8" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC8" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD8" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE8" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF8" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG8" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH8" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI8" s="72" t="s">
+      <c r="Z8" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA8" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB8" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC8" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD8" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE8" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF8" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG8" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH8" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI8" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -20626,70 +20692,70 @@
       <c r="M9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N9" s="71" t="s">
+      <c r="N9" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P9" s="71" t="s">
+      <c r="P9" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R9" s="71" t="s">
+      <c r="R9" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T9" s="71" t="s">
+      <c r="T9" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V9" s="71" t="s">
+      <c r="V9" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X9" s="71" t="s">
+      <c r="X9" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z9" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA9" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB9" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC9" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD9" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE9" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF9" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG9" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH9" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI9" s="72" t="s">
+      <c r="Z9" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB9" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC9" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD9" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE9" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF9" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG9" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH9" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI9" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -20733,70 +20799,70 @@
       <c r="M10" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N10" s="71" t="s">
+      <c r="N10" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P10" s="71" t="s">
+      <c r="P10" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R10" s="71" t="s">
+      <c r="R10" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T10" s="71" t="s">
+      <c r="T10" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V10" s="71" t="s">
+      <c r="V10" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X10" s="71" t="s">
+      <c r="X10" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z10" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA10" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB10" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC10" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD10" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE10" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF10" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG10" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH10" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI10" s="72" t="s">
+      <c r="Z10" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA10" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB10" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD10" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE10" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF10" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG10" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH10" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI10" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -20840,70 +20906,70 @@
       <c r="M11" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="71" t="s">
+      <c r="N11" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O11" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P11" s="71" t="s">
+      <c r="P11" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q11" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R11" s="71" t="s">
+      <c r="R11" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S11" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T11" s="71" t="s">
+      <c r="T11" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U11" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V11" s="71" t="s">
+      <c r="V11" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W11" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X11" s="71" t="s">
+      <c r="X11" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y11" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z11" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA11" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB11" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC11" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD11" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE11" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF11" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG11" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH11" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI11" s="72" t="s">
+      <c r="Z11" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA11" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB11" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC11" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD11" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE11" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF11" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG11" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH11" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI11" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -20947,70 +21013,70 @@
       <c r="M12" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N12" s="71" t="s">
+      <c r="N12" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O12" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P12" s="71" t="s">
+      <c r="P12" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q12" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R12" s="71" t="s">
+      <c r="R12" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S12" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T12" s="71" t="s">
+      <c r="T12" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U12" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V12" s="71" t="s">
+      <c r="V12" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W12" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X12" s="71" t="s">
+      <c r="X12" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y12" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z12" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA12" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB12" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC12" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD12" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE12" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF12" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG12" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH12" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI12" s="72" t="s">
+      <c r="Z12" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA12" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB12" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC12" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD12" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE12" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF12" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG12" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH12" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI12" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -21054,70 +21120,70 @@
       <c r="M13" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N13" s="71" t="s">
+      <c r="N13" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O13" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P13" s="71" t="s">
+      <c r="P13" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q13" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="71" t="s">
+      <c r="R13" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S13" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T13" s="71" t="s">
+      <c r="T13" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U13" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V13" s="71" t="s">
+      <c r="V13" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W13" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X13" s="71" t="s">
+      <c r="X13" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y13" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z13" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA13" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB13" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC13" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD13" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE13" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF13" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG13" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH13" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI13" s="72" t="s">
+      <c r="Z13" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA13" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB13" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC13" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD13" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE13" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF13" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG13" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH13" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI13" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -21161,70 +21227,70 @@
       <c r="M14" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N14" s="71" t="s">
+      <c r="N14" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O14" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P14" s="71" t="s">
+      <c r="P14" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q14" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R14" s="71" t="s">
+      <c r="R14" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S14" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T14" s="71" t="s">
+      <c r="T14" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U14" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V14" s="71" t="s">
+      <c r="V14" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W14" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X14" s="71" t="s">
+      <c r="X14" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y14" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z14" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA14" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB14" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC14" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD14" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE14" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF14" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG14" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH14" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI14" s="72" t="s">
+      <c r="Z14" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA14" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB14" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC14" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD14" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE14" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF14" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG14" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH14" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI14" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -21268,70 +21334,70 @@
       <c r="M15" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N15" s="71" t="s">
+      <c r="N15" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O15" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P15" s="71" t="s">
+      <c r="P15" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q15" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R15" s="71" t="s">
+      <c r="R15" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S15" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T15" s="71" t="s">
+      <c r="T15" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U15" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V15" s="71" t="s">
+      <c r="V15" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W15" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X15" s="71" t="s">
+      <c r="X15" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y15" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z15" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA15" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB15" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC15" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD15" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE15" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF15" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG15" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH15" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI15" s="72" t="s">
+      <c r="Z15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA15" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC15" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE15" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG15" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI15" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -21375,70 +21441,70 @@
       <c r="M16" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N16" s="71" t="s">
+      <c r="N16" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O16" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P16" s="71" t="s">
+      <c r="P16" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q16" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R16" s="71" t="s">
+      <c r="R16" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S16" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T16" s="71" t="s">
+      <c r="T16" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U16" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V16" s="71" t="s">
+      <c r="V16" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W16" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X16" s="71" t="s">
+      <c r="X16" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y16" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z16" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA16" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB16" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC16" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD16" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE16" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF16" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG16" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH16" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI16" s="72" t="s">
+      <c r="Z16" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA16" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB16" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC16" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD16" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE16" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF16" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG16" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH16" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI16" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -21482,70 +21548,70 @@
       <c r="M17" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N17" s="71" t="s">
+      <c r="N17" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O17" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P17" s="71" t="s">
+      <c r="P17" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q17" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R17" s="71" t="s">
+      <c r="R17" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S17" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T17" s="71" t="s">
+      <c r="T17" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U17" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V17" s="71" t="s">
+      <c r="V17" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W17" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X17" s="71" t="s">
+      <c r="X17" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y17" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z17" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA17" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB17" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC17" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD17" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE17" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF17" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG17" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH17" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI17" s="72" t="s">
+      <c r="Z17" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA17" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB17" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC17" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD17" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE17" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF17" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG17" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH17" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI17" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -21589,70 +21655,70 @@
       <c r="M18" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N18" s="71" t="s">
+      <c r="N18" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O18" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P18" s="71" t="s">
+      <c r="P18" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q18" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R18" s="71" t="s">
+      <c r="R18" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S18" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T18" s="71" t="s">
+      <c r="T18" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U18" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V18" s="71" t="s">
+      <c r="V18" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W18" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X18" s="71" t="s">
+      <c r="X18" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y18" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z18" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA18" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB18" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC18" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD18" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE18" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF18" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG18" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH18" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI18" s="72" t="s">
+      <c r="Z18" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA18" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB18" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC18" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD18" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE18" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF18" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG18" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH18" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI18" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -21696,70 +21762,70 @@
       <c r="M19" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N19" s="71" t="s">
+      <c r="N19" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O19" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P19" s="71" t="s">
+      <c r="P19" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q19" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R19" s="71" t="s">
+      <c r="R19" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S19" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T19" s="71" t="s">
+      <c r="T19" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U19" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V19" s="71" t="s">
+      <c r="V19" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W19" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X19" s="71" t="s">
+      <c r="X19" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y19" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z19" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA19" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB19" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC19" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD19" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE19" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF19" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG19" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH19" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI19" s="72" t="s">
+      <c r="Z19" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA19" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC19" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD19" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE19" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF19" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG19" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH19" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI19" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -21803,70 +21869,70 @@
       <c r="M20" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N20" s="71" t="s">
+      <c r="N20" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O20" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P20" s="71" t="s">
+      <c r="P20" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q20" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R20" s="71" t="s">
+      <c r="R20" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S20" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T20" s="71" t="s">
+      <c r="T20" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U20" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V20" s="71" t="s">
+      <c r="V20" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W20" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X20" s="71" t="s">
+      <c r="X20" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y20" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z20" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA20" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB20" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC20" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD20" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE20" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF20" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG20" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH20" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI20" s="72" t="s">
+      <c r="Z20" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA20" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB20" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC20" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD20" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE20" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF20" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG20" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH20" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI20" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -21910,70 +21976,70 @@
       <c r="M21" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N21" s="71" t="s">
+      <c r="N21" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O21" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P21" s="71" t="s">
+      <c r="P21" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q21" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R21" s="71" t="s">
+      <c r="R21" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S21" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T21" s="71" t="s">
+      <c r="T21" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U21" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V21" s="71" t="s">
+      <c r="V21" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W21" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X21" s="71" t="s">
+      <c r="X21" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y21" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z21" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA21" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB21" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC21" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD21" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE21" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF21" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG21" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH21" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI21" s="72" t="s">
+      <c r="Z21" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA21" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB21" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC21" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD21" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE21" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF21" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG21" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH21" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI21" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22017,70 +22083,70 @@
       <c r="M22" s="18" t="s">
         <v>855</v>
       </c>
-      <c r="N22" s="71" t="s">
+      <c r="N22" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O22" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P22" s="71" t="s">
+      <c r="P22" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q22" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R22" s="71" t="s">
+      <c r="R22" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S22" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T22" s="71" t="s">
+      <c r="T22" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U22" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V22" s="71" t="s">
+      <c r="V22" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W22" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X22" s="71" t="s">
+      <c r="X22" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y22" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z22" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA22" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB22" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC22" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD22" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE22" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF22" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG22" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH22" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI22" s="72" t="s">
+      <c r="Z22" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA22" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB22" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC22" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD22" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE22" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF22" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG22" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH22" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI22" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22124,70 +22190,70 @@
       <c r="M23" s="18" t="s">
         <v>845</v>
       </c>
-      <c r="N23" s="71" t="s">
+      <c r="N23" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O23" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P23" s="71" t="s">
+      <c r="P23" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q23" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R23" s="71" t="s">
+      <c r="R23" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S23" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T23" s="71" t="s">
+      <c r="T23" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U23" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V23" s="71" t="s">
+      <c r="V23" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W23" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X23" s="71" t="s">
+      <c r="X23" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y23" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z23" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA23" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB23" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC23" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD23" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE23" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF23" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG23" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH23" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI23" s="72" t="s">
+      <c r="Z23" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA23" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB23" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC23" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD23" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE23" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF23" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG23" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH23" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI23" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22231,70 +22297,70 @@
       <c r="M24" s="18" t="s">
         <v>846</v>
       </c>
-      <c r="N24" s="71" t="s">
+      <c r="N24" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O24" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P24" s="71" t="s">
+      <c r="P24" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q24" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R24" s="71" t="s">
+      <c r="R24" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S24" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T24" s="71" t="s">
+      <c r="T24" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U24" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V24" s="71" t="s">
+      <c r="V24" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W24" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X24" s="71" t="s">
+      <c r="X24" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y24" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z24" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA24" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB24" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC24" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD24" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE24" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF24" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG24" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH24" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI24" s="72" t="s">
+      <c r="Z24" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA24" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB24" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC24" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD24" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE24" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF24" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG24" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH24" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI24" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22338,70 +22404,70 @@
       <c r="M25" s="18" t="s">
         <v>845</v>
       </c>
-      <c r="N25" s="71" t="s">
+      <c r="N25" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O25" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P25" s="71" t="s">
+      <c r="P25" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q25" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R25" s="71" t="s">
+      <c r="R25" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S25" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T25" s="71" t="s">
+      <c r="T25" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U25" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V25" s="71" t="s">
+      <c r="V25" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W25" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X25" s="71" t="s">
+      <c r="X25" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y25" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z25" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA25" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB25" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC25" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD25" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE25" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF25" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG25" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH25" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI25" s="72" t="s">
+      <c r="Z25" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA25" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB25" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC25" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD25" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE25" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF25" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG25" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH25" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI25" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22445,70 +22511,70 @@
       <c r="M26" s="18" t="s">
         <v>847</v>
       </c>
-      <c r="N26" s="71" t="s">
+      <c r="N26" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O26" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P26" s="71" t="s">
+      <c r="P26" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q26" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R26" s="71" t="s">
+      <c r="R26" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S26" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T26" s="71" t="s">
+      <c r="T26" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U26" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V26" s="71" t="s">
+      <c r="V26" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W26" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X26" s="71" t="s">
+      <c r="X26" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y26" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z26" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA26" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB26" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC26" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD26" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE26" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF26" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG26" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH26" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI26" s="72" t="s">
+      <c r="Z26" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA26" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB26" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC26" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD26" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE26" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF26" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG26" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH26" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI26" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22552,70 +22618,70 @@
       <c r="M27" s="18" t="s">
         <v>847</v>
       </c>
-      <c r="N27" s="71" t="s">
+      <c r="N27" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O27" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P27" s="71" t="s">
+      <c r="P27" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q27" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R27" s="71" t="s">
+      <c r="R27" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S27" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T27" s="71" t="s">
+      <c r="T27" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U27" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V27" s="71" t="s">
+      <c r="V27" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W27" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X27" s="71" t="s">
+      <c r="X27" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y27" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z27" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA27" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB27" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC27" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD27" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE27" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF27" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG27" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH27" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI27" s="72" t="s">
+      <c r="Z27" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA27" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB27" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC27" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD27" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE27" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF27" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG27" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH27" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI27" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22659,70 +22725,70 @@
       <c r="M28" s="18" t="s">
         <v>847</v>
       </c>
-      <c r="N28" s="71" t="s">
+      <c r="N28" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O28" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P28" s="71" t="s">
+      <c r="P28" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q28" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R28" s="71" t="s">
+      <c r="R28" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S28" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T28" s="71" t="s">
+      <c r="T28" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U28" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V28" s="71" t="s">
+      <c r="V28" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W28" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X28" s="71" t="s">
+      <c r="X28" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y28" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z28" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA28" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB28" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC28" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD28" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE28" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF28" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG28" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH28" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI28" s="72" t="s">
+      <c r="Z28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC28" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE28" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG28" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH28" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI28" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22766,70 +22832,70 @@
       <c r="M29" s="18" t="s">
         <v>848</v>
       </c>
-      <c r="N29" s="71" t="s">
+      <c r="N29" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O29" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P29" s="71" t="s">
+      <c r="P29" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q29" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R29" s="71" t="s">
+      <c r="R29" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S29" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T29" s="71" t="s">
+      <c r="T29" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U29" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V29" s="71" t="s">
+      <c r="V29" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W29" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X29" s="71" t="s">
+      <c r="X29" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y29" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z29" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA29" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB29" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC29" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD29" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE29" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF29" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG29" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH29" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI29" s="72" t="s">
+      <c r="Z29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA29" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE29" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG29" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH29" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI29" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22873,70 +22939,70 @@
       <c r="M30" s="18" t="s">
         <v>849</v>
       </c>
-      <c r="N30" s="71" t="s">
+      <c r="N30" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O30" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P30" s="71" t="s">
+      <c r="P30" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q30" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R30" s="71" t="s">
+      <c r="R30" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S30" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T30" s="71" t="s">
+      <c r="T30" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U30" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V30" s="71" t="s">
+      <c r="V30" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W30" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X30" s="71" t="s">
+      <c r="X30" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y30" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z30" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA30" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB30" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC30" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD30" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE30" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF30" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG30" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH30" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI30" s="72" t="s">
+      <c r="Z30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA30" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE30" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG30" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH30" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI30" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -22980,70 +23046,70 @@
       <c r="M31" s="18" t="s">
         <v>850</v>
       </c>
-      <c r="N31" s="71" t="s">
+      <c r="N31" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O31" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P31" s="71" t="s">
+      <c r="P31" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q31" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R31" s="71" t="s">
+      <c r="R31" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S31" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T31" s="71" t="s">
+      <c r="T31" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U31" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V31" s="71" t="s">
+      <c r="V31" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W31" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X31" s="71" t="s">
+      <c r="X31" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y31" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z31" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA31" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB31" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC31" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD31" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE31" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF31" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG31" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH31" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI31" s="72" t="s">
+      <c r="Z31" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA31" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB31" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD31" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE31" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF31" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG31" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH31" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI31" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -23087,610 +23153,610 @@
       <c r="M32" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N32" s="71" t="s">
+      <c r="N32" s="70" t="s">
         <v>9</v>
       </c>
       <c r="O32" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="P32" s="71" t="s">
+      <c r="P32" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Q32" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="R32" s="71" t="s">
+      <c r="R32" s="70" t="s">
         <v>9</v>
       </c>
       <c r="S32" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="T32" s="71" t="s">
+      <c r="T32" s="70" t="s">
         <v>9</v>
       </c>
       <c r="U32" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="V32" s="71" t="s">
+      <c r="V32" s="70" t="s">
         <v>9</v>
       </c>
       <c r="W32" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="X32" s="71" t="s">
+      <c r="X32" s="70" t="s">
         <v>9</v>
       </c>
       <c r="Y32" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z32" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA32" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB32" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC32" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD32" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE32" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF32" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG32" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH32" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI32" s="72" t="s">
+      <c r="Z32" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA32" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB32" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC32" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD32" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE32" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF32" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG32" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH32" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI32" s="71" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:35" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:35" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="16">
         <v>33</v>
       </c>
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="62" t="s">
+        <v>892</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>927</v>
+      </c>
+      <c r="D33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>897</v>
+      </c>
+      <c r="H33" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I33" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L33" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="M33" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="N33" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="O33" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="P33" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q33" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="R33" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="S33" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="T33" s="28" t="s">
         <v>893</v>
       </c>
-      <c r="C33" s="58" t="s">
-        <v>891</v>
-      </c>
-      <c r="D33" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>898</v>
-      </c>
-      <c r="H33" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="I33" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J33" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="K33" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="L33" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="M33" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="N33" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="O33" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="P33" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q33" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="R33" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="S33" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="T33" s="28" t="s">
+      <c r="U33" s="18" t="s">
         <v>894</v>
       </c>
-      <c r="U33" s="18" t="s">
+      <c r="V33" s="28" t="s">
         <v>895</v>
       </c>
-      <c r="V33" s="28" t="s">
+      <c r="W33" s="18" t="s">
         <v>896</v>
       </c>
-      <c r="W33" s="18" t="s">
-        <v>897</v>
-      </c>
-      <c r="X33" s="65" t="str">
+      <c r="X33" s="64" t="str">
         <f t="shared" ref="X33:X37" si="0">IF(Y33="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="Y33" s="66" t="s">
-        <v>899</v>
-      </c>
-      <c r="Z33" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA33" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB33" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC33" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD33" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE33" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF33" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG33" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH33" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI33" s="72" t="s">
+      <c r="Y33" s="65" t="s">
+        <v>898</v>
+      </c>
+      <c r="Z33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA33" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC33" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE33" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG33" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH33" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI33" s="71" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:35" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:35" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
         <v>34</v>
       </c>
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="62" t="s">
+        <v>899</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>927</v>
+      </c>
+      <c r="D34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>901</v>
+      </c>
+      <c r="H34" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I34" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="K34" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L34" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="M34" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="N34" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="O34" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="P34" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q34" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="R34" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="S34" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="T34" s="28" t="s">
+        <v>893</v>
+      </c>
+      <c r="U34" s="18" t="s">
+        <v>894</v>
+      </c>
+      <c r="V34" s="28" t="s">
+        <v>895</v>
+      </c>
+      <c r="W34" s="18" t="s">
         <v>900</v>
       </c>
-      <c r="C34" s="58" t="s">
-        <v>891</v>
-      </c>
-      <c r="D34" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>902</v>
-      </c>
-      <c r="H34" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="I34" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J34" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="K34" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="L34" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="M34" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="N34" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="O34" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="P34" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q34" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="R34" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="S34" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="T34" s="28" t="s">
-        <v>894</v>
-      </c>
-      <c r="U34" s="18" t="s">
-        <v>895</v>
-      </c>
-      <c r="V34" s="28" t="s">
-        <v>896</v>
-      </c>
-      <c r="W34" s="18" t="s">
-        <v>901</v>
-      </c>
-      <c r="X34" s="65" t="str">
+      <c r="X34" s="64" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Y34" s="66" t="s">
-        <v>903</v>
-      </c>
-      <c r="Z34" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA34" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB34" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC34" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD34" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE34" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF34" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG34" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH34" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI34" s="72" t="s">
+      <c r="Y34" s="65" t="s">
+        <v>902</v>
+      </c>
+      <c r="Z34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA34" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC34" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE34" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG34" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH34" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI34" s="71" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:35" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:35" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
         <v>35</v>
       </c>
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="62" t="s">
+        <v>903</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>927</v>
+      </c>
+      <c r="D35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>905</v>
+      </c>
+      <c r="H35" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I35" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J35" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="K35" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L35" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="M35" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="N35" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="O35" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="P35" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q35" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="R35" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="S35" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="T35" s="28" t="s">
+        <v>893</v>
+      </c>
+      <c r="U35" s="18" t="s">
+        <v>894</v>
+      </c>
+      <c r="V35" s="28" t="s">
+        <v>895</v>
+      </c>
+      <c r="W35" s="18" t="s">
         <v>904</v>
       </c>
-      <c r="C35" s="58" t="s">
-        <v>891</v>
-      </c>
-      <c r="D35" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="G35" s="18" t="s">
-        <v>906</v>
-      </c>
-      <c r="H35" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="I35" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J35" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="K35" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="L35" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="M35" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="N35" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="O35" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="P35" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q35" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="R35" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="S35" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="T35" s="28" t="s">
-        <v>894</v>
-      </c>
-      <c r="U35" s="18" t="s">
-        <v>895</v>
-      </c>
-      <c r="V35" s="28" t="s">
-        <v>896</v>
-      </c>
-      <c r="W35" s="18" t="s">
-        <v>905</v>
-      </c>
-      <c r="X35" s="65" t="str">
+      <c r="X35" s="64" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Y35" s="66" t="s">
-        <v>907</v>
-      </c>
-      <c r="Z35" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA35" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB35" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC35" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD35" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE35" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF35" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG35" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH35" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI35" s="72" t="s">
+      <c r="Y35" s="65" t="s">
+        <v>906</v>
+      </c>
+      <c r="Z35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA35" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC35" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE35" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG35" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH35" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI35" s="71" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:35" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:35" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="16">
         <v>36</v>
       </c>
-      <c r="B36" s="63" t="s">
+      <c r="B36" s="62" t="s">
+        <v>907</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>927</v>
+      </c>
+      <c r="D36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>909</v>
+      </c>
+      <c r="H36" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I36" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J36" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="K36" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L36" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="M36" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="N36" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="O36" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="P36" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q36" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="R36" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="S36" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="T36" s="28" t="s">
+        <v>893</v>
+      </c>
+      <c r="U36" s="18" t="s">
+        <v>894</v>
+      </c>
+      <c r="V36" s="28" t="s">
+        <v>895</v>
+      </c>
+      <c r="W36" s="18" t="s">
         <v>908</v>
       </c>
-      <c r="C36" s="58" t="s">
-        <v>891</v>
-      </c>
-      <c r="D36" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>910</v>
-      </c>
-      <c r="H36" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="I36" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J36" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="K36" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="L36" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="M36" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="N36" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="O36" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="P36" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q36" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="R36" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="S36" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="T36" s="28" t="s">
-        <v>894</v>
-      </c>
-      <c r="U36" s="18" t="s">
-        <v>895</v>
-      </c>
-      <c r="V36" s="28" t="s">
-        <v>896</v>
-      </c>
-      <c r="W36" s="18" t="s">
-        <v>909</v>
-      </c>
-      <c r="X36" s="65" t="str">
+      <c r="X36" s="64" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Y36" s="66" t="s">
-        <v>911</v>
-      </c>
-      <c r="Z36" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA36" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB36" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC36" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD36" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE36" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF36" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG36" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH36" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI36" s="72" t="s">
+      <c r="Y36" s="65" t="s">
+        <v>910</v>
+      </c>
+      <c r="Z36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA36" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC36" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE36" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG36" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH36" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI36" s="71" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:35" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:35" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="16">
         <v>37</v>
       </c>
-      <c r="B37" s="63" t="s">
+      <c r="B37" s="62" t="s">
+        <v>911</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>927</v>
+      </c>
+      <c r="D37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>913</v>
+      </c>
+      <c r="H37" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I37" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J37" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="K37" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L37" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="M37" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="N37" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="O37" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="P37" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q37" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="R37" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="S37" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="T37" s="28" t="s">
+        <v>893</v>
+      </c>
+      <c r="U37" s="18" t="s">
+        <v>894</v>
+      </c>
+      <c r="V37" s="28" t="s">
+        <v>895</v>
+      </c>
+      <c r="W37" s="18" t="s">
         <v>912</v>
       </c>
-      <c r="C37" s="58" t="s">
-        <v>891</v>
-      </c>
-      <c r="D37" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="G37" s="18" t="s">
-        <v>914</v>
-      </c>
-      <c r="H37" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="I37" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J37" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="K37" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="L37" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="M37" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="N37" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="O37" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="P37" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q37" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="R37" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="S37" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="T37" s="28" t="s">
-        <v>894</v>
-      </c>
-      <c r="U37" s="18" t="s">
-        <v>895</v>
-      </c>
-      <c r="V37" s="28" t="s">
-        <v>896</v>
-      </c>
-      <c r="W37" s="18" t="s">
-        <v>913</v>
-      </c>
-      <c r="X37" s="65" t="str">
+      <c r="X37" s="64" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Y37" s="66" t="s">
-        <v>915</v>
-      </c>
-      <c r="Z37" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA37" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB37" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC37" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD37" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE37" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF37" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG37" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH37" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI37" s="72" t="s">
+      <c r="Y37" s="65" t="s">
+        <v>914</v>
+      </c>
+      <c r="Z37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA37" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC37" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE37" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG37" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH37" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI37" s="71" t="s">
         <v>9</v>
       </c>
     </row>
@@ -23700,18 +23766,18 @@
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="B1:B32 B38:B1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B32 B1 B5:B23">
-    <cfRule type="duplicateValues" dxfId="4" priority="563"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:AI37">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
